--- a/artfynd/A 25670-2026 artfynd.xlsx
+++ b/artfynd/A 25670-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232500</v>
       </c>
       <c r="B2" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>134232498</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>134232499</v>
       </c>
       <c r="B4" t="n">
-        <v>98052</v>
+        <v>98059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25670-2026 artfynd.xlsx
+++ b/artfynd/A 25670-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134232500</v>
+        <v>134232498</v>
       </c>
       <c r="B2" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707199</v>
+        <v>706941</v>
       </c>
       <c r="R2" t="n">
-        <v>7335307</v>
+        <v>7335434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232498</v>
+        <v>134232500</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>706941</v>
+        <v>707199</v>
       </c>
       <c r="R3" t="n">
-        <v>7335434</v>
+        <v>7335307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>134232499</v>
       </c>
       <c r="B4" t="n">
-        <v>98059</v>
+        <v>98066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25670-2026 artfynd.xlsx
+++ b/artfynd/A 25670-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232498</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>